--- a/www/download/COUNTRY.TWN.rpA1.xlsx
+++ b/www/download/COUNTRY.TWN.rpA1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>China: Taiwan</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>26.4760398769361</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>27.4574416266748</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>28.6615076395938</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>33.4448165399382</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>32.2684732083258</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>31.2207295837448</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>33.7952018675018</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>34.578145867322</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>34.4234076826823</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>33.4224592164426</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>32.1646824788283</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>32.5309040569911</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>32.8407230902673</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>31.5169997719211</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>33.0489991420892</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.368</t>
+          <t>0.062695292159292</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.275</t>
+          <t>0.0142090738834881</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>0.132975317397294</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.425</t>
+          <t>0.193768000904363</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9.458</t>
+          <t>0.230959601842029</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.597</t>
+          <t>0.171488493511917</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9.383</t>
+          <t>0.157580013608353</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.454</t>
+          <t>0.200302856519808</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9.574</t>
+          <t>0.213570421239554</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9.784</t>
+          <t>0.252932502849065</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9.943</t>
+          <t>0.30228815754608</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.113</t>
+          <t>0.363582207248398</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10.292</t>
+          <t>0.551435721679693</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>10.404</t>
+          <t>0.590676301699707</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>10.279</t>
+          <t>0.779240908231389</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.476</t>
+          <t>0.658182605722093</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.448</t>
+          <t>0.566577538723551</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6.585</t>
+          <t>0.777635588411477</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6.664</t>
+          <t>0.862644236946448</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.722</t>
+          <t>0.91986877697804</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.855</t>
+          <t>0.839671114942814</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>0.799478729052185</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.774</t>
+          <t>0.856179036262401</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6.923</t>
+          <t>0.866477586793467</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7.165</t>
+          <t>0.909588606978349</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7.366</t>
+          <t>0.942148877245942</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>7.553</t>
+          <t>1.03631742050102</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>7.745</t>
+          <t>1.29009023840461</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>1.33648070439672</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>7.907</t>
+          <t>1.58894045300099</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21651.582</t>
+          <t>1.21998387562969</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21306.613</t>
+          <t>1.07337565711928</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21621.853</t>
+          <t>1.38272250507798</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21389.203</t>
+          <t>1.49386985721618</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21466.651</t>
+          <t>1.55811985990355</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21802.7</t>
+          <t>1.46700591995909</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20446.521</t>
+          <t>1.37426590717862</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20645.819</t>
+          <t>1.43425894353407</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20895.479</t>
+          <t>1.4511484978703</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21547.134</t>
+          <t>1.48559276366758</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>21808.029</t>
+          <t>1.48670951606781</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>22052.318</t>
+          <t>1.57607891256304</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>22426.051</t>
+          <t>1.86018443404034</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>22584.97</t>
+          <t>1.85939172364223</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>21729.434</t>
+          <t>2.29666926281316</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15097.83</t>
+          <t>35201902046.143</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14946.957</t>
+          <t>34282705691.6782</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15293.409</t>
+          <t>33485580730.2434</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15229.189</t>
+          <t>32485302326.1341</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15348.731</t>
+          <t>32503713473.7268</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15665.324</t>
+          <t>35045388388.5817</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14693.148</t>
+          <t>31561866733.1824</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14840.401</t>
+          <t>33233243160.8725</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15160.842</t>
+          <t>34765031408.9777</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15843.53</t>
+          <t>38799019165.9553</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>16187.971</t>
+          <t>37529336579.7969</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>16526.11</t>
+          <t>38417690302.8861</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16946.724</t>
+          <t>38381296916.031</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>17266.618</t>
+          <t>38688752166.8158</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>16712.116</t>
+          <t>31734106552.5513</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>9113995785.50573</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>9657874385.65693</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>8775299622.09746</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>8397601046.59968</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>8296313588.49171</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>8910149130.50167</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>8659550796.17721</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>33.36</t>
+          <t>8541101148.25489</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>8711029839.86232</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>8912351190.90533</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>8985528665.73859</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>8845456883.36856</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>8100793255.18308</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>8202818547.43782</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>7193986561.1959</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>2587429.59922393</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31.16</t>
+          <t>2475563.19753159</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>2410942.83317165</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>2630328.22069678</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>2474758.72045507</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>2488629.80452836</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>2628416.15345284</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>2686701.04845028</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>2618017.00711066</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>2522390.79644355</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>2300628.42481512</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>2198118.34496425</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>2053138.83642006</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>1939549.38513771</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>1903112.28633618</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>98077.866479483</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>96488.0295543096</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>97420.8260615106</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>95265.9928311138</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>98085.8702333103</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>100723.261834864</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>90388.5079323237</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>92133.3264670608</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>32.72</t>
+          <t>99997.6986835373</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>112809.108581469</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>122538.602429538</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>129465.346954009</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>149511.25189947</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>166119.999364368</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>145371.275696418</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>274026.187858561</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>268867.76866624</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>260930.259815024</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>251764.348497001</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>262348.698572258</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>288721.917794981</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>253186.308664362</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>272531.725457419</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>307117.919099833</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>377747.363251336</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>391317.669688746</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>419854.285699805</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>474483.636621961</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>529546.088937987</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>405174.505123604</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>0.656554443487451</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>0.547644569426972</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>0.742779137154988</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33.54</t>
+          <t>0.813516650961366</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>0.850066338621485</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>0.758143907118317</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>0.6967563232137</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>35.23</t>
+          <t>0.737527801532134</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>0.740419015985979</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>0.77770485367161</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>0.801560164970953</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>0.868316209859665</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>1.09198331509608</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>1.10496161107426</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>1.3230673874809</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>37840.9451226263</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>39172.5425932418</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42526.5860996838</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>43035.5940772088</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>49723.1898636696</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>58566.5527948832</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>53069.9843390756</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>52521.9195117726</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>55437.0219881852</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>63853.6183875367</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>66840.5141894893</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>67763.8504520565</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>73131.7358711163</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>33.07</t>
+          <t>80320.2970282769</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>76776.1213821351</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26.4760398769361</t>
+          <t>1407.40919917889</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27.4574416266748</t>
+          <t>1497.75546366019</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>28.6615076395938</t>
+          <t>1332.60324968303</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33.4448165399382</t>
+          <t>1260.0844531871</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>32.2684732083258</t>
+          <t>1234.17788632222</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>31.2207295837448</t>
+          <t>1299.71630205089</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>33.7952018675018</t>
+          <t>1286.78213739323</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>34.578145867322</t>
+          <t>1260.82166531287</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>34.4234076826823</t>
+          <t>1258.31840454317</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>33.4224592164426</t>
+          <t>1243.83965360636</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>32.1646824788283</t>
+          <t>1219.91842599256</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>32.5309040569911</t>
+          <t>1171.05776398763</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>32.8407230902673</t>
+          <t>1045.97152873317</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>31.5169997719211</t>
+          <t>1034.445476791</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>33.0489991420892</t>
+          <t>909.813828473363</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>6332365388.95019</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>7822119689.08011</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>6524409731.4774</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>6019879706.96133</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>6553299937.41912</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>7659224919.88652</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>8187739509.70191</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>9246215816.86967</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>9222879936.36033</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>8886355345.31277</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>8882663708.27408</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>8656860875.06019</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>7915306404.53287</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>6593880183.64378</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>6235939128.07758</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>6871053173.13554</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>8493625698.3625</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>7209393793.93394</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>6925192666.57753</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>7433820122.41982</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>8818470455.29495</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>9228382555.70082</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>10316781545.2217</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>10385431177.417</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>10296310566.5323</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>10288588967.9556</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>10114484620.2274</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>9307915492.52753</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>7965560577.71107</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>7294875815.867</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>-538687784.18535</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>-671506009.282388</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>-684984062.456533</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>-905312959.616194</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>-880520185.000706</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>-1159245535.40844</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>-1040643045.99891</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>-1070565728.35206</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>-1162551241.05664</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>-1409955221.21952</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>-1405925259.6815</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>-1457623745.16721</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-1392609087.99466</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.064</t>
+          <t>-1371680394.06729</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>-1058936687.78942</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>2331.4499627049</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>2317.99310966326</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>2322.43314165253</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>2285.18413747236</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>2283.31096335576</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>2285.08829743312</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>2183.3557282204</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>2190.71269625516</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>2190.00127943207</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>2211.17978940523</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>2197.75644078226</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>2187.9062031401</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>2188.15498617534</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>2177.46801739446</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>2113.55883360561</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>2311.22781700245</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>2297.20897702561</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>2302.64672055581</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>2269.41144436844</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>2269.68182682928</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>2271.82450946322</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>2179.10270536632</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>2183.8184258317</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>2182.52335437893</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>2202.28271852868</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>2193.30476720352</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>2180.59108610194</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>2178.97890532983</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>2170.79684476025</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>2113.96384683028</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>126915.300584837</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>133807.570225189</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>141549.403621721</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>129583.20936143</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>140573.515905248</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>171723.904470568</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>145946.618825458</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>156566.353351376</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>172957.536973781</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>206297.20752308</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>226720.555872909</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>250928.003961118</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>277126.017640646</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>288769.510145104</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>77.92</t>
+          <t>229938.549269187</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>10018570701.0081</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>10249362060.8811</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.76</t>
+          <t>10623657753.3645</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>10332956780.6082</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>91.99</t>
+          <t>10590784609.6227</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>83.97</t>
+          <t>12543939883.0737</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>79.95</t>
+          <t>11332141771.8078</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>85.62</t>
+          <t>12016967768.0219</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>86.65</t>
+          <t>13031386349.849</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>14893221920.2217</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>94.21</t>
+          <t>15035622663.5322</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>103.63</t>
+          <t>16030262385.2921</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>129.01</t>
+          <t>16242655719.7508</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>133.65</t>
+          <t>15975511133.1847</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>158.89</t>
+          <t>13149376071.3956</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>115491.205204335</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>107.34</t>
+          <t>116964.727993192</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>126404.927715789</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>149.39</t>
+          <t>118725.571668396</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>155.81</t>
+          <t>125228.890666358</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>155143.66271924</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>137.43</t>
+          <t>123737.886028629</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>143.43</t>
+          <t>128581.844309189</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>145.11</t>
+          <t>142925.572710745</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>148.56</t>
+          <t>185090.771689476</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>148.67</t>
+          <t>200893.328272577</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>157.61</t>
+          <t>218687.456232123</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>186.02</t>
+          <t>235846.043363277</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>185.94</t>
+          <t>258045.085694861</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>229.67</t>
+          <t>189322.125283643</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21651.582</t>
+          <t>14586853457.3604</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21306.613</t>
+          <t>15574922934.2613</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21621.853</t>
+          <t>15075534926.9464</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21389.203</t>
+          <t>14788744505.8929</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21466.651</t>
+          <t>14883760807.8278</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>21802.7</t>
+          <t>17741769954.4187</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20446.521</t>
+          <t>16053012566.6019</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>20645.819</t>
+          <t>16943351089.1149</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20895.479</t>
+          <t>17880655413.9173</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>21547.134</t>
+          <t>20947561933.4155</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>21808.029</t>
+          <t>20721233743.0332</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>22052.318</t>
+          <t>21047059737.543</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>22426.051</t>
+          <t>20048465106.3348</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>22584.97</t>
+          <t>19862133783.7847</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>21729.434</t>
+          <t>15450252284.9046</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15097.83</t>
+          <t>11424.0953805027</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>14946.957</t>
+          <t>16842.8422319973</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15293.409</t>
+          <t>15144.4759059314</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15229.189</t>
+          <t>10857.6376930343</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15348.731</t>
+          <t>15344.6252388895</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>15665.324</t>
+          <t>16580.2417513284</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14693.148</t>
+          <t>22208.7327968289</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14840.401</t>
+          <t>27984.5090421867</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>15160.842</t>
+          <t>30031.9642630362</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>15843.53</t>
+          <t>21206.4358336036</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>16187.971</t>
+          <t>25827.2276003316</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>16526.11</t>
+          <t>32240.5477289959</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>16946.724</t>
+          <t>41279.9742773682</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>17266.618</t>
+          <t>30724.4244502436</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>16712.116</t>
+          <t>40616.4239855442</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>35201.902</t>
+          <t>-4568282756.35238</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>34282.706</t>
+          <t>-5325560873.38016</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>33485.581</t>
+          <t>-4451877173.58193</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>32485.302</t>
+          <t>-4455787725.28471</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>32503.713</t>
+          <t>-4292976198.20511</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>35045.388</t>
+          <t>-5197830071.34494</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31561.867</t>
+          <t>-4720870794.79403</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>33233.243</t>
+          <t>-4926383321.09299</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>34765.031</t>
+          <t>-4849269064.06827</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>38799.019</t>
+          <t>-6054340013.19372</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>37529.337</t>
+          <t>-5685611079.50095</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>38417.69</t>
+          <t>-5016797352.25083</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>38381.297</t>
+          <t>-3805809386.58399</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>38688.752</t>
+          <t>-3886622650.59998</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>31734.107</t>
+          <t>-2300876213.50907</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>115885.19263</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>120899.79259</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>122402.31903</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>111252.9351</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>117455.72698</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>121887.86232</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>107332.51486</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>111310.5662</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>112697.38423</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>120663.95146</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>127889.89906</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>131144.28038</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>139969.05593</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>133690.32676</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>127911.08753</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>12599.261</t>
+          <t>0.105268843803967</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12302.965</t>
+          <t>0.115713310351518</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12502.164</t>
+          <t>0.119765472648056</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>12292.227</t>
+          <t>0.114393255856194</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12152.357</t>
+          <t>0.109815170168258</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12225.902</t>
+          <t>0.100895389063207</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11267.711</t>
+          <t>0.0973426790902998</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11234.983</t>
+          <t>0.112147313142895</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>11319.506</t>
+          <t>0.104438739623569</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>11586.799</t>
+          <t>0.0955865599994396</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>11752.07</t>
+          <t>0.0949477876831069</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>11846.395</t>
+          <t>0.0917519742672653</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>12094.065</t>
+          <t>0.0961898461420713</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>12136.763</t>
+          <t>0.0746390784801517</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>11385.779</t>
+          <t>0.0776081605524416</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>139276.624928551</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>146385.999045722</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>149823.721510242</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>134565.297386867</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>143785.405090095</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>154526.466639178</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>141412.000266344</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>137943.195527433</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>142429.711039491</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>152115.099336601</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>165805.900278924</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>172048.156420619</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>175788.537823953</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>183824.014436678</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>169371.52751886</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9113.996</t>
+          <t>170674.531036294</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9657.874</t>
+          <t>179262.534251722</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8775.3</t>
+          <t>182091.650982684</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>8397.601</t>
+          <t>164311.131679755</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8296.314</t>
+          <t>176098.037946597</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8910.149</t>
+          <t>188365.268356586</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8659.551</t>
+          <t>171574.566746385</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8541.101</t>
+          <t>167528.333807679</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8711.03</t>
+          <t>172506.401579701</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8912.351</t>
+          <t>184264.398670204</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>8985.529</t>
+          <t>200746.334689084</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>8845.457</t>
+          <t>207723.236472464</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>8100.793</t>
+          <t>211172.142171429</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>8202.819</t>
+          <t>220585.827149092</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>7193.987</t>
+          <t>203574.600826775</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>504927.311922058</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>516427.067409121</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>538741.153781766</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>517485.758141669</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>575972.257501595</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>75.81</t>
+          <t>634283.138830458</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>603069.804562106</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>612526.70345318</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>74.04</t>
+          <t>655216.869322225</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>77.77</t>
+          <t>761752.847290309</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>817496.487232387</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>86.83</t>
+          <t>872795.86096111</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>109.2</t>
+          <t>930138.657206178</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>1064420.98925107</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>132.31</t>
+          <t>1002614.26620783</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.587</t>
+          <t>170674.531036294</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.476</t>
+          <t>182782.359036392</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.411</t>
+          <t>189687.876484339</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>195584.619276153</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.475</t>
+          <t>202943.629853673</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.489</t>
+          <t>208005.46861129</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>204855.427334524</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.687</t>
+          <t>204723.854000435</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.618</t>
+          <t>207934.802040712</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.522</t>
+          <t>209993.349097749</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.301</t>
+          <t>218498.744024458</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.198</t>
+          <t>224995.141507731</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.053</t>
+          <t>228990.543360731</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>225733.673686465</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.903</t>
+          <t>222874.170231128</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>139276.624928551</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>149580.772791529</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>156280.98911373</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>160744.107966953</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>166692.618398156</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>171465.578402718</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>169299.65409321</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>168927.202540183</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>171967.546960885</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>173757.91829522</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>181001.525914776</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>186544.612446131</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>190964.353713897</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>188647.256825312</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>186258.695058692</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>90994.0594537061</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>98930.0281182777</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>107049.175017316</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>102232.474810245</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>112973.681333403</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>122562.796863414</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>111774.414793615</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>121215.143532321</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>123867.046000299</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>136666.952629796</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>144459.997090916</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>147844.593827536</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>162601.630198571</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>159767.698780908</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>154587.170326161</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>15097830216.4054</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>14946956845.1698</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>15293409103.6755</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>15229189326.1391</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>15348730504.7165</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>15665324405.3071</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>14693147569.6039</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>14840400700.7909</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>15160841982.1177</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>15843529969.6984</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>16187970505.3992</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>16526110478.8122</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>16946724328.8859</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>17266618144.9646</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>16712115566.2901</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>21651582189.6789</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>21306613261.9126</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>21621852706.019</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>21389202863.1726</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>21466650718.1514</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>21802699817.3186</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20446520684.4522</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>20645819397.8129</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>20895478594.8239</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>21547134118.0846</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>21808029300.3046</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>22052317653.749</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>22426050893.6546</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>22584970372.8856</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>21729434381.5685</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>12599260952.7067</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>12302964897.5388</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>12502164134.5941</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>12292227223.5654</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>12152356917.4732</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>12225901856.4505</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>11267710551.2568</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>11234982776.9988</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>11319506024.7481</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>11586798987.223</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>11752069509.8024</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>11846394746.0835</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>12094064596.8221</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>12136763200.818</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>11385779446.3724</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9368000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>9275000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>9390000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>9425000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>9458000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9597000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9383000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9454000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9574000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9784000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9943000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>10113000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>10292000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10404000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>10279000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6475725.60334481</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6448231.78414933</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>6585080.46125861</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6664316.05068995</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6722137.61114634</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6855456.93044083</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6729616.88271473</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6774234.12305928</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>6922754.85156308</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>7165193.00945672</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>7365679.92931801</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>7553390.75098092</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>7744755.02693112</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>7929677.04096322</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>7907097.403946</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>21651582189.6789</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>21306613261.9126</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>21621852706.019</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>21389202863.1726</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>21466650718.1514</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>21802699817.3186</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20446520684.4522</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>20645819397.8129</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>20895478594.8239</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>21547134118.0846</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>21808029300.3046</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>22052317653.749</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>22426050893.6546</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>22584970372.8856</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>21729434381.5685</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>15097830216.4054</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>14946956845.1698</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>15293409103.6755</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>15229189326.1391</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>15348730504.7165</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>15665324405.3071</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>14693147569.6039</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>14840400700.7909</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>15160841982.1177</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>15843529969.6984</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>16187970505.3992</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>16526110478.8122</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16946724328.8859</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>17266618144.9646</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>16712115566.2901</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.278661046608263</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.287068902069005</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.295280418344885</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.303300390719474</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.311133312462363</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.318783395141901</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.326254586924336</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.333550589078339</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.341414762121223</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.349165485148323</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.354232247339983</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.372099401365079</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.366770912127975</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.380458193364835</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.412754001468868</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.308343832456194</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.311591700769992</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.314870815048877</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.31818036630264</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.321519643434556</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.324888026905767</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.328284983091023</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.331710059251875</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.331430527503408</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.33119171473992</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.32956276626521</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.32336906100886</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.329465738342722</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.325787181809133</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.332430771654221</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.412995120935543</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.401339397161003</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.389848766606239</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.378519242977886</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.367347044103081</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.356328577952332</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.345460429984641</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.334739351669787</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.327154710375368</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.319642800111757</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.316204986394807</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.304531537626061</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.303763349529303</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.293754624826032</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.254815226876912</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.214223984649701</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.221762082415447</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.229300180181193</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.236838277946938</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.244376375712684</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.25191447347843</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.259452571244176</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.266990669009922</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.274297445852658</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.281604222695395</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.289922249231759</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.308288891565255</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.304642425381812</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.317551555991869</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.341667640070491</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.3227469521659</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.32697344651853</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.33119994087116</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.335426435223791</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.339652929576421</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.343879423929051</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.348105918281681</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.352332412634311</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.352659077651124</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.352985742667937</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.35040809984152</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.345171811253209</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.351305333899944</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.351708638479808</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.357530055963773</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.463029063184399</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.451264471066023</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.439499878947647</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.427735286829271</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.415970694710895</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.404206102592519</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.392441510474143</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.380676918355767</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.373043476496218</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.365410034636669</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.359669650926721</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.346539297181535</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.344052240718244</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.330739805528323</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.300802303965736</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>579827.12367</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>595756.99404</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>617079.60598</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>559258.11173</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>600785.57935</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>667886.93136</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>588049.75076</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>607155.39682</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>642358.59517</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>738392.64111</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>795818.39608</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>837615.21176</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>900791.7699</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>945759.69106</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>810483.6867</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>261668.59049</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>278192.56237</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>289140.826</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>266543.60649</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>289071.71928</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>310928.06522</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>283348.98154</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>288743.47734</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>296373.44758</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>320931.3513</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>345206.33178</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>355567.8303</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>373773.77237</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>380353.52593</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>357822.52825</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>13368475.5407106</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>14531159.0825348</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>15801491.4409056</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>17145061.2032804</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>18435286.2317739</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>19817700.7057358</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20624728.998767</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>21389003.3752959</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>22104438.7933364</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>23091470.7347447</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>24047762.2097772</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>24941454.4203983</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>25794657.7022577</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>26322561.8895612</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>26528061.3447381</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
